--- a/templates/PhieuThu.xlsx
+++ b/templates/PhieuThu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E9F061-DD79-8D4E-83EC-2ACE465C748C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99259A85-EFDD-0445-8CA4-E926E14FD82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11560" yWindow="5700" windowWidth="27640" windowHeight="16940" xr2:uid="{00A52EDA-E189-4842-98A1-92DB2EA8A8D4}"/>
+    <workbookView xWindow="2600" yWindow="2700" windowWidth="27640" windowHeight="16940" xr2:uid="{00A52EDA-E189-4842-98A1-92DB2EA8A8D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -232,6 +232,9 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -243,9 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -287,7 +287,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -684,39 +684,39 @@
   <sheetData>
     <row r="1" spans="1:5" ht="23">
       <c r="A1" s="1"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" spans="1:5" ht="23">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" ht="27" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2"/>
@@ -744,12 +744,12 @@
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="9"/>
@@ -783,12 +783,12 @@
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="17">
         <f>SUM(E10:E10)</f>
         <v>0</v>

--- a/templates/PhieuThu.xlsx
+++ b/templates/PhieuThu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99259A85-EFDD-0445-8CA4-E926E14FD82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C896D29-445B-7345-ABE9-5FF9BCB44681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="2700" windowWidth="27640" windowHeight="16940" xr2:uid="{00A52EDA-E189-4842-98A1-92DB2EA8A8D4}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
   <si>
-    <t>60 Đống Đa, Phường 2, TP. Cao Lãnh, Đồng Tháp</t>
-  </si>
-  <si>
     <t>PHIẾU THU</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
   </si>
   <si>
     <t>Tổng thành tiền</t>
+  </si>
+  <si>
+    <t>60 Đống Đa, Phường Cao Lãnh, Đồng Tháp</t>
   </si>
 </sst>
 </file>
@@ -285,7 +285,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:colOff>609600</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -676,10 +676,10 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="41.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="5" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23">
@@ -694,7 +694,7 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="20" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -703,7 +703,7 @@
     <row r="3" spans="1:5" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
@@ -712,7 +712,7 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -727,13 +727,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="D6" s="7">
         <v>1964</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>7</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>8</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -758,21 +758,21 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5" ht="17">
+    <row r="9" spans="1:5" ht="21" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -784,7 +784,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
